--- a/Data Files/Backoffce/GestaoCreditoDescarteincidencias/GestaoCreditoDescarteincidencias.xlsx
+++ b/Data Files/Backoffce/GestaoCreditoDescarteincidencias/GestaoCreditoDescarteincidencias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GestaoCreditoDescarteincidencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{C168B9E9-E0F1-41B2-BD94-8CE019E72504}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{42683896-2179-40CB-9D37-6A43567295FB}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
     <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="1" r:id="rId2" sheetId="4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">DescarteIncidencia!$A$1:$D$7</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">DescarteIncidencia!$A$1:$D$1</definedName>
     <definedName name="Base">#REF!</definedName>
     <definedName name="TAB">#REF!</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="75">
   <si>
     <t>Status</t>
   </si>
@@ -57,199 +57,199 @@
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>749302489</t>
-  </si>
-  <si>
-    <t>656836479</t>
-  </si>
-  <si>
-    <t>653500102</t>
-  </si>
-  <si>
-    <t>681285759</t>
-  </si>
-  <si>
-    <t>674818517</t>
-  </si>
-  <si>
-    <t>672334590</t>
-  </si>
-  <si>
-    <t>634329076</t>
-  </si>
-  <si>
-    <t>627043544</t>
-  </si>
-  <si>
-    <t>615808361</t>
-  </si>
-  <si>
-    <t>749087593</t>
-  </si>
-  <si>
-    <t>591217561</t>
-  </si>
-  <si>
-    <t>572807794</t>
-  </si>
-  <si>
-    <t>756556787</t>
-  </si>
-  <si>
-    <t>749547836</t>
-  </si>
-  <si>
-    <t>749413104</t>
-  </si>
-  <si>
-    <t>742372257</t>
-  </si>
-  <si>
-    <t>737434591</t>
-  </si>
-  <si>
-    <t>736425103</t>
-  </si>
-  <si>
-    <t>736410006</t>
-  </si>
-  <si>
-    <t>736398854</t>
-  </si>
-  <si>
-    <t>724887710</t>
-  </si>
-  <si>
-    <t>723176628</t>
-  </si>
-  <si>
-    <t>715328724</t>
-  </si>
-  <si>
-    <t>691229367</t>
-  </si>
-  <si>
-    <t>691023018</t>
-  </si>
-  <si>
-    <t>714241621</t>
-  </si>
-  <si>
-    <t>708135680</t>
-  </si>
-  <si>
-    <t>696773468</t>
-  </si>
-  <si>
-    <t>621659220</t>
-  </si>
-  <si>
-    <t>630842023</t>
-  </si>
-  <si>
-    <t>613834898</t>
-  </si>
-  <si>
-    <t>752397665</t>
-  </si>
-  <si>
-    <t>571357411</t>
-  </si>
-  <si>
-    <t>722050154</t>
-  </si>
-  <si>
-    <t>738503196</t>
-  </si>
-  <si>
-    <t>672947037</t>
-  </si>
-  <si>
-    <t>741249381</t>
-  </si>
-  <si>
-    <t>540093808</t>
-  </si>
-  <si>
-    <t>737669139</t>
-  </si>
-  <si>
-    <t>613556202</t>
-  </si>
-  <si>
-    <t>748828070</t>
-  </si>
-  <si>
-    <t>630063893</t>
-  </si>
-  <si>
-    <t>609730472</t>
-  </si>
-  <si>
-    <t>737608442</t>
-  </si>
-  <si>
-    <t>705818668</t>
-  </si>
-  <si>
-    <t>717930014</t>
-  </si>
-  <si>
-    <t>507402570</t>
-  </si>
-  <si>
-    <t>747723587</t>
-  </si>
-  <si>
-    <t>684734340</t>
-  </si>
-  <si>
-    <t>633131234</t>
-  </si>
-  <si>
-    <t>568297190</t>
-  </si>
-  <si>
-    <t>585467339</t>
-  </si>
-  <si>
-    <t>747408627</t>
-  </si>
-  <si>
-    <t>694546569</t>
-  </si>
-  <si>
-    <t>175246499</t>
-  </si>
-  <si>
-    <t>173858998</t>
-  </si>
-  <si>
-    <t>749024752</t>
-  </si>
-  <si>
-    <t>749138792</t>
-  </si>
-  <si>
-    <t>748455593</t>
-  </si>
-  <si>
-    <t>743986543</t>
-  </si>
-  <si>
-    <t>747239287</t>
-  </si>
-  <si>
-    <t>747235681</t>
-  </si>
-  <si>
-    <t>747234528</t>
-  </si>
-  <si>
-    <t>747233421</t>
-  </si>
-  <si>
-    <t>715785329</t>
+    <t>910534779</t>
+  </si>
+  <si>
+    <t>882913894</t>
+  </si>
+  <si>
+    <t>868487335</t>
+  </si>
+  <si>
+    <t>743754784</t>
+  </si>
+  <si>
+    <t>739095366</t>
+  </si>
+  <si>
+    <t>730995689</t>
+  </si>
+  <si>
+    <t>673922880</t>
+  </si>
+  <si>
+    <t>845699549</t>
+  </si>
+  <si>
+    <t>832130557</t>
+  </si>
+  <si>
+    <t>808477123</t>
+  </si>
+  <si>
+    <t>799103845</t>
+  </si>
+  <si>
+    <t>777755251</t>
+  </si>
+  <si>
+    <t>911573602</t>
+  </si>
+  <si>
+    <t>911617904</t>
+  </si>
+  <si>
+    <t>796051070</t>
+  </si>
+  <si>
+    <t>799021955</t>
+  </si>
+  <si>
+    <t>798414151</t>
+  </si>
+  <si>
+    <t>792454393</t>
+  </si>
+  <si>
+    <t>781538818</t>
+  </si>
+  <si>
+    <t>683880029</t>
+  </si>
+  <si>
+    <t>720069701</t>
+  </si>
+  <si>
+    <t>761918295</t>
+  </si>
+  <si>
+    <t>717254597</t>
+  </si>
+  <si>
+    <t>711856926</t>
+  </si>
+  <si>
+    <t>704515364</t>
+  </si>
+  <si>
+    <t>698957606</t>
+  </si>
+  <si>
+    <t>695253371</t>
+  </si>
+  <si>
+    <t>857342368</t>
+  </si>
+  <si>
+    <t>851220339</t>
+  </si>
+  <si>
+    <t>809770195</t>
+  </si>
+  <si>
+    <t>911106445</t>
+  </si>
+  <si>
+    <t>910816333</t>
+  </si>
+  <si>
+    <t>910223571</t>
+  </si>
+  <si>
+    <t>910221195</t>
+  </si>
+  <si>
+    <t>909062469</t>
+  </si>
+  <si>
+    <t>909015947</t>
+  </si>
+  <si>
+    <t>905770438</t>
+  </si>
+  <si>
+    <t>905214692</t>
+  </si>
+  <si>
+    <t>902834104</t>
+  </si>
+  <si>
+    <t>902021892</t>
+  </si>
+  <si>
+    <t>899791275</t>
+  </si>
+  <si>
+    <t>899048809</t>
+  </si>
+  <si>
+    <t>897167213</t>
+  </si>
+  <si>
+    <t>890855475</t>
+  </si>
+  <si>
+    <t>899108462</t>
+  </si>
+  <si>
+    <t>698785726</t>
+  </si>
+  <si>
+    <t>735618450</t>
+  </si>
+  <si>
+    <t>877245252</t>
+  </si>
+  <si>
+    <t>882402146</t>
+  </si>
+  <si>
+    <t>809789088</t>
+  </si>
+  <si>
+    <t>801137781</t>
+  </si>
+  <si>
+    <t>774743490</t>
+  </si>
+  <si>
+    <t>765840602</t>
+  </si>
+  <si>
+    <t>857561249</t>
+  </si>
+  <si>
+    <t>825948148</t>
+  </si>
+  <si>
+    <t>902295868</t>
+  </si>
+  <si>
+    <t>840243210</t>
+  </si>
+  <si>
+    <t>902087711</t>
+  </si>
+  <si>
+    <t>903269359</t>
+  </si>
+  <si>
+    <t>901795157</t>
+  </si>
+  <si>
+    <t>901687867</t>
+  </si>
+  <si>
+    <t>901686463</t>
+  </si>
+  <si>
+    <t>800032199</t>
+  </si>
+  <si>
+    <t>902425630</t>
+  </si>
+  <si>
+    <t>711491872</t>
   </si>
   <si>
     <t>Processado</t>
@@ -266,7 +266,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;* #,##0.00_-;\-&quot;R$&quot;* #,##0.00_-;_-&quot;R$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,12 +288,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -370,7 +364,7 @@
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="43"/>
     <xf applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0" borderId="0" fillId="0" fontId="1" numFmtId="164"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="4" fontId="2" numFmtId="49" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,13 +381,10 @@
     <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -416,9 +407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
@@ -456,7 +447,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
@@ -562,7 +553,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -704,7 +695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -720,16 +711,16 @@
   <cols>
     <col min="1" max="1" customWidth="true" style="4" width="38.0" collapsed="true"/>
     <col min="2" max="2" customWidth="true" style="5" width="64.85546875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="7" width="14.5703125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="6" width="14.5703125" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="5" width="75.140625" collapsed="true"/>
     <col min="5" max="16384" style="5" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row customFormat="1" r="1" s="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -744,12 +735,12 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" t="s">
         <v>74</v>
       </c>
     </row>
@@ -758,12 +749,12 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -777,7 +768,7 @@
       <c r="C4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" t="s">
         <v>74</v>
       </c>
     </row>
@@ -791,7 +782,7 @@
       <c r="C5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" t="s">
         <v>74</v>
       </c>
     </row>
@@ -805,7 +796,7 @@
       <c r="C6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -819,7 +810,7 @@
       <c r="C7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -833,7 +824,7 @@
       <c r="C8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" t="s">
         <v>74</v>
       </c>
     </row>
@@ -847,7 +838,7 @@
       <c r="C9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -861,7 +852,7 @@
       <c r="C10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" t="s">
         <v>74</v>
       </c>
     </row>
@@ -875,7 +866,7 @@
       <c r="C11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" t="s">
         <v>74</v>
       </c>
     </row>
@@ -889,7 +880,7 @@
       <c r="C12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -903,7 +894,7 @@
       <c r="C13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -917,7 +908,7 @@
       <c r="C14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" t="s">
         <v>74</v>
       </c>
     </row>
@@ -926,12 +917,12 @@
         <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" t="s">
         <v>74</v>
       </c>
     </row>
@@ -940,35 +931,35 @@
         <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>73</v>
@@ -977,12 +968,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>73</v>
@@ -991,12 +982,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>73</v>
@@ -1005,12 +996,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>73</v>
@@ -1019,12 +1010,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>73</v>
@@ -1033,12 +1024,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>73</v>
@@ -1047,12 +1038,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>73</v>
@@ -1061,12 +1052,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>73</v>
@@ -1075,12 +1066,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>73</v>
@@ -1089,12 +1080,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>73</v>
@@ -1103,7 +1094,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -1117,7 +1108,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -1131,7 +1122,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>36</v>
       </c>
@@ -1145,7 +1136,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>37</v>
       </c>
@@ -1159,7 +1150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>38</v>
       </c>
@@ -1220,7 +1211,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>73</v>
@@ -1234,7 +1225,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>73</v>
@@ -1248,7 +1239,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>73</v>
@@ -1262,7 +1253,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>73</v>
@@ -1276,7 +1267,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>73</v>
@@ -1290,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>73</v>
@@ -1304,7 +1295,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>73</v>
@@ -1318,7 +1309,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>73</v>
@@ -1332,7 +1323,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>73</v>
@@ -1346,7 +1337,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>73</v>
@@ -1360,7 +1351,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>73</v>
@@ -1374,7 +1365,7 @@
         <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>73</v>
@@ -1388,7 +1379,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>73</v>
@@ -1402,7 +1393,7 @@
         <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>73</v>
@@ -1416,7 +1407,7 @@
         <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>73</v>
@@ -1430,7 +1421,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>73</v>
@@ -1444,7 +1435,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>73</v>
@@ -1458,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>73</v>
@@ -1472,7 +1463,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>73</v>
@@ -1486,7 +1477,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>73</v>
@@ -1500,7 +1491,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>73</v>
@@ -1514,7 +1505,7 @@
         <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>73</v>
@@ -1528,7 +1519,7 @@
         <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>73</v>
@@ -1542,7 +1533,7 @@
         <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>73</v>
@@ -1556,7 +1547,7 @@
         <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>73</v>
@@ -1570,7 +1561,7 @@
         <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>73</v>
@@ -1584,7 +1575,7 @@
         <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>73</v>
@@ -1598,7 +1589,7 @@
         <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>73</v>
@@ -1640,7 +1631,7 @@
         <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>73</v>
@@ -1650,8 +1641,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
   <pageSetup horizontalDpi="300" orientation="portrait" paperSize="9" r:id="rId1" verticalDpi="300"/>
   <headerFooter>
